--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,83 +1570,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>4003945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>478071.91</t>
+          <t>4003945.1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>452191</t>
+          <t>478071.91</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>453079</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>25880.91</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>24992.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1084,12 +1084,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1219,12 +1219,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1246,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1300,12 +1300,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1462,12 +1462,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1597,83 +1597,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4003945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>478071.91</t>
+          <t>4003945.1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>453079</t>
+          <t>478071.91</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>475720</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>24992.91</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2351.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,7 +384,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1126,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1192,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1219,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1234,7 +1249,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1246,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1261,7 +1276,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1273,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1288,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1300,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1315,7 +1330,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1327,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1354,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1369,7 +1384,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1381,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1396,7 +1411,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1408,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1435,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1450,7 +1465,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1462,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1489,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1624,83 +1639,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>4003945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>478071.91</t>
+          <t>4133945.1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>475720</t>
+          <t>493925.56</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>475720</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2351.91</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>18205.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1126,12 +1126,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1234,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1288,12 +1288,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1450,12 +1450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1477,12 +1477,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,12 +1639,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,83 +1666,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>4133945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>493925.56</t>
+          <t>4133945.1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>475720</t>
+          <t>493925.56</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>491573</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>18205.56</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2352.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1168,7 +1183,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1234,12 +1249,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1261,12 +1276,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1288,12 +1303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1303,7 +1318,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1315,12 +1330,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1330,7 +1345,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1342,12 +1357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1357,7 +1372,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1369,12 +1384,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1384,7 +1399,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1396,12 +1411,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1438,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1438,7 +1453,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1450,12 +1465,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1465,7 +1480,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1477,12 +1492,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1504,12 +1519,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1519,7 +1534,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1531,12 +1546,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1693,83 +1708,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>4133945.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>493925.56</t>
+          <t>4143905.1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>491573</t>
+          <t>494831.02</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>491573</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2352.56</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3258.02</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1210,7 +1225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1276,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1303,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1330,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1345,7 +1360,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1357,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1387,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1384,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1399,7 +1414,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1411,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1438,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1465,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1480,7 +1495,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1492,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1507,7 +1522,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1519,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1546,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1561,7 +1576,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1573,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1615,7 +1630,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1735,83 +1750,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>4143905.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>494831.02</t>
+          <t>4173905.1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>491573</t>
+          <t>498489.56</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>491573</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>3258.02</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>6916.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1210,12 +1210,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1318,12 +1318,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1372,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1399,12 +1399,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1426,12 +1426,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1453,12 +1453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1480,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1588,12 +1588,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1777,83 +1777,110 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>4173905.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>498489.56</t>
+          <t>4173905.1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>491573</t>
+          <t>498489.56</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>495231</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>6916.56</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3258.56</t>
         </is>
       </c>
     </row>
